--- a/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56703</t>
+          <t>56617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>47503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91118</t>
+          <t>92155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112357</t>
+          <t>114183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>475</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>30716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83299</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68922</t>
+          <t>68607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70949</t>
+          <t>70317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74350</t>
+          <t>77523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129024</t>
+          <t>129052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79163</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112516</t>
+          <t>110704</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40617</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>76371</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34969</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53792</t>
+          <t>52765</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46078</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>77871</t>
+          <t>78187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>42154</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54119</t>
+          <t>59007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34181</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>34338</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33455</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>48845</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64558</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>397</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>70624</t>
+          <t>71027</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>56428</t>
+          <t>56394</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>77798</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>63253</t>
+          <t>62676</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>69587</t>
+          <t>70322</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>91995</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>125478</t>
+          <t>124537</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>46497</t>
+          <t>47299</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>40336</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>75331</t>
+          <t>75406</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>75339</t>
+          <t>75856</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>93662</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>96109</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>117305</t>
+          <t>116741</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>178011</t>
+          <t>178688</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>205964</t>
+          <t>206334</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>952</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>131762</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>105673</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,47 +7331,47 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>184903</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>164197</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>184903</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>160068</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>208894</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>277124</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>340459</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>267540</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>338461</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>589720</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>677064</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100131</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>214550</t>
+          <t>210399</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>142995</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>201674</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>324572</t>
+          <t>316091</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>66370</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2779</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8178</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13259</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8005</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13035</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8931</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2796</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7663</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4036</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13364</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8941</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43148</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36562</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49166</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>48408</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41043</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56617</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>103389</t>
+          <t>76452</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92155</t>
+          <t>67824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>84291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>405</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1398,57 +1398,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4778</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5711</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13366</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6796</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3175</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13891</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37343</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27423</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49777</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26018</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37808</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40746</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55373</t>
+          <t>34403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66764</t>
+          <t>63526</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>50055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85678</t>
+          <t>76539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>52933</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>41980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68607</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70317</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>109022</t>
+          <t>102315</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77523</t>
+          <t>88852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129052</t>
+          <t>118006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10096</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>37260</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10639</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>81633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>11340</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16749</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7802</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2817</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13949</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10379</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -2193,57 +2193,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2578</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2581</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4349</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9892</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9253</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>9,03%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5119</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>14123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14489</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10133</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>20223</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>11781</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7980</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17361</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20799</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36552</t>
+          <t>33506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30011</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23621</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>36009</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>33964</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>28030</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>39591</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>58,29%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>67,95%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40617</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>63157</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>71330</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2258</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5881</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5955</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -2988,57 +2988,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>783</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9232</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>18938</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>26,24%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>22908</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10371</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>40648</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>52544</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>23862</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14712</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>33790</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>33,07%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>38942</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>31361</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>46477</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>55,52%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>44,71%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25855</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>62368</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>74983</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3437</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>34538</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>8902</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4895</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>13889</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59007</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>5214</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>2508</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6946</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -3783,57 +3783,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1607</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>4373</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>12113</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>5960</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>3086</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -4352,107 +4352,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4578,57 +4578,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>16767</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>11543</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>34,26%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>23,59%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>45,22%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>8546</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>13391</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>23831</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>18912</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>29754</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>48,69%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>29781</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>24723</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>34619</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>53,55%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>74,99%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>54120</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>48845</t>
+          <t>46967</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>61364</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,79%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>251</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>4528</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>11059</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>9405</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -5373,57 +5373,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5490,72 +5490,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>9726</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>6105</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>15595</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>5654</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>14997</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>12287</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>14750</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>35489</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>26362</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>45856</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>19983</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>13325</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>30950</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>67016</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>38114</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>28961</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>50305</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>35,91%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>19879</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>13458</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>27407</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>56394</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>61843</t>
+          <t>58607</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>48340</t>
+          <t>46848</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>75175</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>45917</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>36699</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>55722</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>52718</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>42795</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>62676</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>54706</t>
+          <t>52982</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>70322</t>
+          <t>62812</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>107424</t>
+          <t>98899</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>85317</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>124537</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>9625</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>22837</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>19508</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>13083</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>28205</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25837</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>47299</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -6055,107 +6055,107 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>5450</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5307</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -6168,57 +6168,57 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6285,107 +6285,107 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2889</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>3621</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6398,72 +6398,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>6367</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>12546</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -6511,72 +6511,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>33459</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>23619</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>43474</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>27,27%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>30463</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>23369</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>40645</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>34938</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>22515</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>40557</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>68396</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>50209</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>75406</t>
+          <t>83394</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -6624,72 +6624,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>106526</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>95113</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>117202</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>66,82%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>59,66%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>85648</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>75856</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>93662</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>57,63%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>106707</t>
+          <t>90419</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>79701</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>100961</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>192355</t>
+          <t>196945</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>178688</t>
+          <t>181293</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>206334</t>
+          <t>210020</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -6737,72 +6737,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>10846</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>18131</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>12428</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>7983</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>18994</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -6850,72 +6850,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>5526</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6963,57 +6963,57 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7080,107 +7080,107 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>17625</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>21777</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>18889</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>34831</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>28225</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>37083</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7193,72 +7193,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -7306,72 +7306,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>174766</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>152743</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>199469</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>125424</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>105673</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>145262</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>184903</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>164197</t>
+          <t>114351</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>211456</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>277124</t>
+          <t>277603</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>340671</t>
+          <t>337157</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -7419,72 +7419,72 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>301731</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>277875</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>327411</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>312307</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>268662</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>339342</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>51,12%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>300735</t>
+          <t>293352</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>354232</t>
+          <t>336033</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>639441</t>
+          <t>616087</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>589720</t>
+          <t>582175</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>678934</t>
+          <t>648423</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -7532,57 +7532,57 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>91293</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>76625</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>120786</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>100131</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>210399</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>89148</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>104111</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>238583</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>200740</t>
+          <t>159353</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>316091</t>
+          <t>211488</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -7645,72 +7645,72 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>24051</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>17939</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>33343</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>24488</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>18261</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>33730</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>38154</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -7758,57 +7758,57 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">

--- a/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Provincia-trans_orig.xlsx
@@ -999,7 +999,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1492,7 +1492,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -1993,7 +1993,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2494,7 +2494,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2987,7 +2987,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -3408,7 +3408,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -3909,7 +3909,7 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
@@ -4394,7 +4394,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
@@ -4895,7 +4895,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
